--- a/backend/data/financials_by_company/0A7.F.xlsx
+++ b/backend/data/financials_by_company/0A7.F.xlsx
@@ -667,590 +667,590 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-28609.082535</v>
+        <v>-24129.520995</v>
       </c>
       <c r="C2" t="n">
-        <v>0.056844</v>
+        <v>0.073339</v>
       </c>
       <c r="D2" t="n">
-        <v>10183199</v>
+        <v>5473090</v>
       </c>
       <c r="E2" t="n">
-        <v>-503287</v>
+        <v>-329013</v>
       </c>
       <c r="F2" t="n">
-        <v>-503287</v>
+        <v>-329013</v>
       </c>
       <c r="G2" t="n">
-        <v>1232992</v>
+        <v>860722</v>
       </c>
       <c r="H2" t="n">
-        <v>7208640</v>
+        <v>3766278</v>
       </c>
       <c r="I2" t="n">
-        <v>13654009</v>
+        <v>2264187</v>
       </c>
       <c r="J2" t="n">
-        <v>9679912</v>
+        <v>5144077</v>
       </c>
       <c r="K2" t="n">
-        <v>2471272</v>
+        <v>1377799</v>
       </c>
       <c r="L2" t="n">
-        <v>-1112667</v>
+        <v>-232039</v>
       </c>
       <c r="M2" t="n">
-        <v>1059015</v>
+        <v>240125</v>
       </c>
       <c r="N2" t="n">
-        <v>402756</v>
+        <v>8086</v>
       </c>
       <c r="O2" t="n">
-        <v>1707669.917465</v>
+        <v>1165605.479005</v>
       </c>
       <c r="P2" t="n">
-        <v>1232992</v>
+        <v>860722</v>
       </c>
       <c r="Q2" t="n">
-        <v>35136229</v>
+        <v>20970903</v>
       </c>
       <c r="R2" t="n">
-        <v>6579750</v>
+        <v>6600000</v>
       </c>
       <c r="S2" t="n">
-        <v>6579750</v>
+        <v>6600000</v>
       </c>
       <c r="T2" t="n">
-        <v>0.187392</v>
+        <v>0.130412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.187392</v>
+        <v>0.130412</v>
       </c>
       <c r="V2" t="n">
-        <v>1232992</v>
+        <v>860722</v>
       </c>
       <c r="W2" t="n">
-        <v>1232992</v>
+        <v>860722</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1232992</v>
+        <v>860722</v>
       </c>
       <c r="Z2" t="n">
-        <v>-98985</v>
+        <v>-193516</v>
       </c>
       <c r="AA2" t="n">
-        <v>1331978</v>
+        <v>1054238</v>
       </c>
       <c r="AB2" t="n">
-        <v>1331978</v>
+        <v>1054238</v>
       </c>
       <c r="AC2" t="n">
-        <v>80279</v>
+        <v>83436</v>
       </c>
       <c r="AD2" t="n">
-        <v>1412257</v>
+        <v>1137674</v>
       </c>
       <c r="AE2" t="n">
-        <v>971624</v>
+        <v>574979</v>
       </c>
       <c r="AF2" t="n">
-        <v>-503287</v>
+        <v>-329013</v>
       </c>
       <c r="AG2" t="n">
-        <v>53175</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>33046</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>648</v>
+      </c>
       <c r="AI2" t="n">
-        <v>450112</v>
+        <v>295319</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-1112667</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>-232039</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-8086</v>
+      </c>
       <c r="AL2" t="n">
-        <v>1059015</v>
+        <v>240125</v>
       </c>
       <c r="AM2" t="n">
-        <v>402756</v>
+        <v>8086</v>
       </c>
       <c r="AN2" t="n">
-        <v>2057068</v>
+        <v>1124256</v>
       </c>
       <c r="AO2" t="n">
-        <v>21482220</v>
+        <v>18706716</v>
       </c>
       <c r="AP2" t="n">
-        <v>3500876</v>
+        <v>267038</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7208640</v>
+        <v>3766278</v>
       </c>
       <c r="AR2" t="n">
-        <v>2550509</v>
+        <v>1036189</v>
       </c>
       <c r="AS2" t="n">
-        <v>4658131</v>
+        <v>2730089</v>
       </c>
       <c r="AT2" t="n">
-        <v>23539288</v>
+        <v>19830972</v>
       </c>
       <c r="AU2" t="n">
-        <v>13654009</v>
+        <v>2264187</v>
       </c>
       <c r="AV2" t="n">
-        <v>37193297</v>
+        <v>22095159</v>
       </c>
       <c r="AW2" t="n">
-        <v>37193297</v>
+        <v>22095159</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-98913.60000000001</v>
+        <v>-95701.239835</v>
       </c>
       <c r="C3" t="n">
-        <v>0.24</v>
+        <v>0.226161</v>
       </c>
       <c r="D3" t="n">
-        <v>8921268</v>
+        <v>7524688</v>
       </c>
       <c r="E3" t="n">
-        <v>-412140</v>
+        <v>-423156</v>
       </c>
       <c r="F3" t="n">
-        <v>-412140</v>
+        <v>-423156</v>
       </c>
       <c r="G3" t="n">
-        <v>1120775</v>
+        <v>1206447</v>
       </c>
       <c r="H3" t="n">
-        <v>6271552</v>
+        <v>4884829</v>
       </c>
       <c r="I3" t="n">
-        <v>17396386</v>
+        <v>16950510</v>
       </c>
       <c r="J3" t="n">
-        <v>8509128</v>
+        <v>7101532</v>
       </c>
       <c r="K3" t="n">
-        <v>2237576</v>
+        <v>2216703</v>
       </c>
       <c r="L3" t="n">
-        <v>-490837</v>
+        <v>-299209</v>
       </c>
       <c r="M3" t="n">
-        <v>847422</v>
+        <v>316231</v>
       </c>
       <c r="N3" t="n">
-        <v>356585</v>
+        <v>17022</v>
       </c>
       <c r="O3" t="n">
-        <v>1434001.4</v>
+        <v>1533901.760165</v>
       </c>
       <c r="P3" t="n">
-        <v>1120775</v>
+        <v>1206447</v>
       </c>
       <c r="Q3" t="n">
-        <v>31689939</v>
+        <v>28487863</v>
       </c>
       <c r="R3" t="n">
-        <v>6796750</v>
+        <v>6752762</v>
       </c>
       <c r="S3" t="n">
-        <v>6796750</v>
+        <v>6752762</v>
       </c>
       <c r="T3" t="n">
-        <v>0.164899</v>
+        <v>0.17866</v>
       </c>
       <c r="U3" t="n">
-        <v>0.164899</v>
+        <v>0.17866</v>
       </c>
       <c r="V3" t="n">
-        <v>1120775</v>
+        <v>1206447</v>
       </c>
       <c r="W3" t="n">
-        <v>1120775</v>
+        <v>1206447</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1120775</v>
+        <v>1206447</v>
       </c>
       <c r="Z3" t="n">
-        <v>-291633</v>
+        <v>-264213</v>
       </c>
       <c r="AA3" t="n">
-        <v>1412408</v>
+        <v>1470660</v>
       </c>
       <c r="AB3" t="n">
-        <v>1412409</v>
+        <v>1470660</v>
       </c>
       <c r="AC3" t="n">
-        <v>-22255</v>
+        <v>429812</v>
       </c>
       <c r="AD3" t="n">
-        <v>1390154</v>
+        <v>1900472</v>
       </c>
       <c r="AE3" t="n">
-        <v>716690</v>
+        <v>566064</v>
       </c>
       <c r="AF3" t="n">
-        <v>-412140</v>
+        <v>-423156</v>
       </c>
       <c r="AG3" t="n">
-        <v>49132</v>
+        <v>38688</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>363008</v>
+        <v>384468</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-490837</v>
+        <v>-299209</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>847422</v>
+        <v>316231</v>
       </c>
       <c r="AM3" t="n">
-        <v>356585</v>
+        <v>17022</v>
       </c>
       <c r="AN3" t="n">
-        <v>1576728</v>
+        <v>2057860</v>
       </c>
       <c r="AO3" t="n">
-        <v>14293553</v>
+        <v>11537353</v>
       </c>
       <c r="AP3" t="n">
-        <v>466804</v>
+        <v>171468</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6271551</v>
+        <v>4884829</v>
       </c>
       <c r="AR3" t="n">
-        <v>2198931</v>
+        <v>1474758</v>
       </c>
       <c r="AS3" t="n">
-        <v>4072620</v>
+        <v>3410071</v>
       </c>
       <c r="AT3" t="n">
-        <v>15870281</v>
+        <v>13595213</v>
       </c>
       <c r="AU3" t="n">
-        <v>17396386</v>
+        <v>16950510</v>
       </c>
       <c r="AV3" t="n">
-        <v>33266667</v>
+        <v>30545723</v>
       </c>
       <c r="AW3" t="n">
-        <v>33266667</v>
+        <v>30545723</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-95701.239835</v>
+        <v>-98913.60000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.226161</v>
+        <v>0.24</v>
       </c>
       <c r="D4" t="n">
-        <v>7524688</v>
+        <v>8921268</v>
       </c>
       <c r="E4" t="n">
-        <v>-423156</v>
+        <v>-412140</v>
       </c>
       <c r="F4" t="n">
-        <v>-423156</v>
+        <v>-412140</v>
       </c>
       <c r="G4" t="n">
-        <v>1206447</v>
+        <v>1120775</v>
       </c>
       <c r="H4" t="n">
-        <v>4884829</v>
+        <v>6271552</v>
       </c>
       <c r="I4" t="n">
-        <v>16950510</v>
+        <v>17396386</v>
       </c>
       <c r="J4" t="n">
-        <v>7101532</v>
+        <v>8509128</v>
       </c>
       <c r="K4" t="n">
-        <v>2216703</v>
+        <v>2237576</v>
       </c>
       <c r="L4" t="n">
-        <v>-299209</v>
+        <v>-490837</v>
       </c>
       <c r="M4" t="n">
-        <v>316231</v>
+        <v>847422</v>
       </c>
       <c r="N4" t="n">
-        <v>17022</v>
+        <v>356585</v>
       </c>
       <c r="O4" t="n">
-        <v>1533901.760165</v>
+        <v>1434001.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1206447</v>
+        <v>1120775</v>
       </c>
       <c r="Q4" t="n">
-        <v>28487863</v>
+        <v>31689939</v>
       </c>
       <c r="R4" t="n">
-        <v>6752762</v>
+        <v>6796750</v>
       </c>
       <c r="S4" t="n">
-        <v>6752762</v>
+        <v>6796750</v>
       </c>
       <c r="T4" t="n">
-        <v>0.17866</v>
+        <v>0.164899</v>
       </c>
       <c r="U4" t="n">
-        <v>0.17866</v>
+        <v>0.164899</v>
       </c>
       <c r="V4" t="n">
-        <v>1206447</v>
+        <v>1120775</v>
       </c>
       <c r="W4" t="n">
-        <v>1206447</v>
+        <v>1120775</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1206447</v>
+        <v>1120775</v>
       </c>
       <c r="Z4" t="n">
-        <v>-264213</v>
+        <v>-291633</v>
       </c>
       <c r="AA4" t="n">
-        <v>1470660</v>
+        <v>1412408</v>
       </c>
       <c r="AB4" t="n">
-        <v>1470660</v>
+        <v>1412409</v>
       </c>
       <c r="AC4" t="n">
-        <v>429812</v>
+        <v>-22255</v>
       </c>
       <c r="AD4" t="n">
-        <v>1900472</v>
+        <v>1390154</v>
       </c>
       <c r="AE4" t="n">
-        <v>566064</v>
+        <v>716690</v>
       </c>
       <c r="AF4" t="n">
-        <v>-423156</v>
+        <v>-412140</v>
       </c>
       <c r="AG4" t="n">
-        <v>38688</v>
+        <v>49132</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>384468</v>
+        <v>363008</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-299209</v>
+        <v>-490837</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>316231</v>
+        <v>847422</v>
       </c>
       <c r="AM4" t="n">
-        <v>17022</v>
+        <v>356585</v>
       </c>
       <c r="AN4" t="n">
-        <v>2057860</v>
+        <v>1576728</v>
       </c>
       <c r="AO4" t="n">
-        <v>11537353</v>
+        <v>14293553</v>
       </c>
       <c r="AP4" t="n">
-        <v>171468</v>
+        <v>466804</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4884829</v>
+        <v>6271551</v>
       </c>
       <c r="AR4" t="n">
-        <v>1474758</v>
+        <v>2198931</v>
       </c>
       <c r="AS4" t="n">
-        <v>3410071</v>
+        <v>4072620</v>
       </c>
       <c r="AT4" t="n">
-        <v>13595213</v>
+        <v>15870281</v>
       </c>
       <c r="AU4" t="n">
-        <v>16950510</v>
+        <v>17396386</v>
       </c>
       <c r="AV4" t="n">
-        <v>30545723</v>
+        <v>33266667</v>
       </c>
       <c r="AW4" t="n">
-        <v>30545723</v>
+        <v>33266667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-24129.520995</v>
+        <v>-28609.082535</v>
       </c>
       <c r="C5" t="n">
-        <v>0.073339</v>
+        <v>0.056844</v>
       </c>
       <c r="D5" t="n">
-        <v>5473090</v>
+        <v>10183199</v>
       </c>
       <c r="E5" t="n">
-        <v>-329013</v>
+        <v>-503287</v>
       </c>
       <c r="F5" t="n">
-        <v>-329013</v>
+        <v>-503287</v>
       </c>
       <c r="G5" t="n">
-        <v>860722</v>
+        <v>1232992</v>
       </c>
       <c r="H5" t="n">
-        <v>3766278</v>
+        <v>7208640</v>
       </c>
       <c r="I5" t="n">
-        <v>2264187</v>
+        <v>13654009</v>
       </c>
       <c r="J5" t="n">
-        <v>5144077</v>
+        <v>9679912</v>
       </c>
       <c r="K5" t="n">
-        <v>1377799</v>
+        <v>2471272</v>
       </c>
       <c r="L5" t="n">
-        <v>-232039</v>
+        <v>-1112667</v>
       </c>
       <c r="M5" t="n">
-        <v>240125</v>
+        <v>1059015</v>
       </c>
       <c r="N5" t="n">
-        <v>8086</v>
+        <v>402756</v>
       </c>
       <c r="O5" t="n">
-        <v>1165605.479005</v>
+        <v>1707669.917465</v>
       </c>
       <c r="P5" t="n">
-        <v>860722</v>
+        <v>1232992</v>
       </c>
       <c r="Q5" t="n">
-        <v>20970903</v>
+        <v>35136229</v>
       </c>
       <c r="R5" t="n">
-        <v>6600000</v>
+        <v>6579750</v>
       </c>
       <c r="S5" t="n">
-        <v>6600000</v>
+        <v>6579750</v>
       </c>
       <c r="T5" t="n">
-        <v>0.130412</v>
+        <v>0.187392</v>
       </c>
       <c r="U5" t="n">
-        <v>0.130412</v>
+        <v>0.187392</v>
       </c>
       <c r="V5" t="n">
-        <v>860722</v>
+        <v>1232992</v>
       </c>
       <c r="W5" t="n">
-        <v>860722</v>
+        <v>1232992</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>860722</v>
+        <v>1232992</v>
       </c>
       <c r="Z5" t="n">
-        <v>-193516</v>
+        <v>-98985</v>
       </c>
       <c r="AA5" t="n">
-        <v>1054238</v>
+        <v>1331978</v>
       </c>
       <c r="AB5" t="n">
-        <v>1054238</v>
+        <v>1331978</v>
       </c>
       <c r="AC5" t="n">
-        <v>83436</v>
+        <v>80279</v>
       </c>
       <c r="AD5" t="n">
-        <v>1137674</v>
+        <v>1412257</v>
       </c>
       <c r="AE5" t="n">
-        <v>574979</v>
+        <v>971624</v>
       </c>
       <c r="AF5" t="n">
-        <v>-329013</v>
+        <v>-503287</v>
       </c>
       <c r="AG5" t="n">
-        <v>33046</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>648</v>
-      </c>
+        <v>53175</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>295319</v>
+        <v>450112</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-232039</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-8086</v>
-      </c>
+        <v>-1112667</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>240125</v>
+        <v>1059015</v>
       </c>
       <c r="AM5" t="n">
-        <v>8086</v>
+        <v>402756</v>
       </c>
       <c r="AN5" t="n">
-        <v>1124256</v>
+        <v>2057068</v>
       </c>
       <c r="AO5" t="n">
-        <v>18706716</v>
+        <v>21482220</v>
       </c>
       <c r="AP5" t="n">
-        <v>267038</v>
+        <v>3500876</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3766278</v>
+        <v>7208640</v>
       </c>
       <c r="AR5" t="n">
-        <v>1036189</v>
+        <v>2550509</v>
       </c>
       <c r="AS5" t="n">
-        <v>2730089</v>
+        <v>4658131</v>
       </c>
       <c r="AT5" t="n">
-        <v>19830972</v>
+        <v>23539288</v>
       </c>
       <c r="AU5" t="n">
-        <v>2264187</v>
+        <v>13654009</v>
       </c>
       <c r="AV5" t="n">
-        <v>22095159</v>
+        <v>37193297</v>
       </c>
       <c r="AW5" t="n">
-        <v>22095159</v>
+        <v>37193297</v>
       </c>
     </row>
   </sheetData>
@@ -1616,812 +1616,812 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>217000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>6579750</v>
+        <v>6600000</v>
       </c>
       <c r="D2" t="n">
-        <v>6796750</v>
+        <v>6600000</v>
       </c>
       <c r="E2" t="n">
-        <v>17418751</v>
+        <v>8576355</v>
       </c>
       <c r="F2" t="n">
-        <v>21695973</v>
+        <v>12063930</v>
       </c>
       <c r="G2" t="n">
-        <v>9511421</v>
+        <v>9178421</v>
       </c>
       <c r="H2" t="n">
-        <v>43223594</v>
+        <v>29930250</v>
       </c>
       <c r="I2" t="n">
-        <v>-3617375</v>
+        <v>-3149556</v>
       </c>
       <c r="J2" t="n">
-        <v>9511421</v>
+        <v>9178421</v>
       </c>
       <c r="K2" t="n">
-        <v>21527621</v>
+        <v>17866320</v>
       </c>
       <c r="L2" t="n">
-        <v>35379303</v>
+        <v>26710173</v>
       </c>
       <c r="M2" t="n">
-        <v>22035658</v>
+        <v>18270744</v>
       </c>
       <c r="N2" t="n">
-        <v>508037</v>
+        <v>404424</v>
       </c>
       <c r="O2" t="n">
-        <v>21527621</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>17866320</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7464720</v>
+      </c>
       <c r="Q2" t="n">
-        <v>66725</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1060360</v>
-      </c>
+        <v>3779272</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>277718</v>
+        <v>860722</v>
       </c>
       <c r="T2" t="n">
-        <v>9043013</v>
+        <v>7464720</v>
       </c>
       <c r="U2" t="n">
-        <v>4075287</v>
+        <v>133500</v>
       </c>
       <c r="V2" t="n">
-        <v>4075287</v>
+        <v>133500</v>
       </c>
       <c r="W2" t="n">
-        <v>45426588</v>
+        <v>28389951</v>
       </c>
       <c r="X2" t="n">
-        <v>16996943</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1</v>
-      </c>
+        <v>11091610</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>156290</v>
+        <v>17751</v>
       </c>
       <c r="AA2" t="n">
-        <v>1934767</v>
+        <v>973708</v>
       </c>
       <c r="AB2" t="n">
-        <v>1054203</v>
+        <v>1256298</v>
       </c>
       <c r="AC2" t="n">
-        <v>13851682</v>
+        <v>8843853</v>
       </c>
       <c r="AD2" t="n">
-        <v>13851682</v>
+        <v>8843853</v>
       </c>
       <c r="AE2" t="n">
-        <v>28429645</v>
+        <v>17298341</v>
       </c>
       <c r="AF2" t="n">
-        <v>4960</v>
+        <v>13049</v>
       </c>
       <c r="AG2" t="n">
-        <v>7844291</v>
+        <v>3220077</v>
       </c>
       <c r="AH2" t="n">
-        <v>7844291</v>
+        <v>3220077</v>
       </c>
       <c r="AI2" t="n">
-        <v>366272</v>
+        <v>235431</v>
       </c>
       <c r="AJ2" t="n">
-        <v>10790849</v>
+        <v>8153569</v>
       </c>
       <c r="AK2" t="n">
-        <v>1779398</v>
+        <v>1982692</v>
       </c>
       <c r="AL2" t="n">
-        <v>528317</v>
+        <v>465946</v>
       </c>
       <c r="AM2" t="n">
-        <v>8483134</v>
+        <v>5704931</v>
       </c>
       <c r="AN2" t="n">
-        <v>67462246</v>
+        <v>46660695</v>
       </c>
       <c r="AO2" t="n">
-        <v>42649975</v>
+        <v>32511910</v>
       </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>25499</v>
+        <v>4812</v>
       </c>
       <c r="AR2" t="n">
-        <v>25499</v>
+        <v>4812</v>
       </c>
       <c r="AS2" t="n">
-        <v>12016200</v>
+        <v>8687899</v>
       </c>
       <c r="AT2" t="n">
-        <v>4794794</v>
+        <v>4982706</v>
       </c>
       <c r="AU2" t="n">
-        <v>7221406</v>
+        <v>3705193</v>
       </c>
       <c r="AV2" t="n">
-        <v>30542122</v>
+        <v>23800676</v>
       </c>
       <c r="AW2" t="n">
-        <v>30542122</v>
+        <v>23800676</v>
       </c>
       <c r="AX2" t="n">
-        <v>145120</v>
+        <v>222764</v>
       </c>
       <c r="AY2" t="n">
-        <v>28855265</v>
+        <v>23390221</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1152762</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>388975</v>
-      </c>
+        <v>187691</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>24812270</v>
+        <v>14148785</v>
       </c>
       <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
-        <v>145003</v>
-      </c>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
-        <v>3499302</v>
+        <v>1158248</v>
       </c>
       <c r="BF2" t="n">
-        <v>623707</v>
+        <v>76416</v>
       </c>
       <c r="BG2" t="n">
-        <v>1138510</v>
+        <v>896521</v>
       </c>
       <c r="BH2" t="n">
-        <v>867610</v>
+        <v>896521</v>
       </c>
       <c r="BI2" t="n">
-        <v>69075</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>201825</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>1150891</v>
+        <v>237856</v>
       </c>
       <c r="BL2" t="n">
-        <v>2001764</v>
+        <v>726442</v>
       </c>
       <c r="BM2" t="n">
-        <v>11330379</v>
+        <v>7165235</v>
       </c>
       <c r="BN2" t="n">
-        <v>4922714</v>
+        <v>3888067</v>
       </c>
       <c r="BO2" t="n">
-        <v>645492</v>
+        <v>400492</v>
       </c>
       <c r="BP2" t="n">
-        <v>4277222</v>
+        <v>3487575</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4272326</v>
+        <v>3484012</v>
       </c>
       <c r="BR2" t="n">
-        <v>4896</v>
+        <v>3562</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>6796750</v>
+        <v>6752762</v>
       </c>
       <c r="D3" t="n">
-        <v>6796750</v>
+        <v>6752762</v>
       </c>
       <c r="E3" t="n">
-        <v>13924887</v>
+        <v>12269952</v>
       </c>
       <c r="F3" t="n">
-        <v>19087277</v>
+        <v>15865385</v>
       </c>
       <c r="G3" t="n">
-        <v>13303923</v>
+        <v>11435076</v>
       </c>
       <c r="H3" t="n">
-        <v>41184560</v>
+        <v>36917562</v>
       </c>
       <c r="I3" t="n">
-        <v>390464</v>
+        <v>-69431</v>
       </c>
       <c r="J3" t="n">
-        <v>13303923</v>
+        <v>11435076</v>
       </c>
       <c r="K3" t="n">
-        <v>22097283</v>
+        <v>21052177</v>
       </c>
       <c r="L3" t="n">
-        <v>34586232</v>
+        <v>32308079</v>
       </c>
       <c r="M3" t="n">
-        <v>22720675</v>
+        <v>21572963</v>
       </c>
       <c r="N3" t="n">
-        <v>623392</v>
+        <v>520786</v>
       </c>
       <c r="O3" t="n">
-        <v>22097283</v>
+        <v>21052177</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
         <v>66725</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>1206447</v>
+      </c>
+      <c r="T3" t="n">
+        <v>8769388</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4048912</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4048912</v>
+      </c>
+      <c r="W3" t="n">
+        <v>32805078</v>
+      </c>
+      <c r="X3" t="n">
+        <v>13556903</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>338000</v>
+      </c>
+      <c r="Z3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="n">
-        <v>1120775</v>
-      </c>
-      <c r="T3" t="n">
-        <v>9043013</v>
-      </c>
-      <c r="U3" t="n">
-        <v>4075287</v>
-      </c>
-      <c r="V3" t="n">
-        <v>4075287</v>
-      </c>
-      <c r="W3" t="n">
-        <v>37168518</v>
-      </c>
-      <c r="X3" t="n">
-        <v>15202316</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>64871</v>
-      </c>
       <c r="AA3" t="n">
-        <v>1482591</v>
+        <v>1037803</v>
       </c>
       <c r="AB3" t="n">
-        <v>1165903</v>
+        <v>1263198</v>
       </c>
       <c r="AC3" t="n">
-        <v>12488949</v>
+        <v>11255902</v>
       </c>
       <c r="AD3" t="n">
-        <v>12488949</v>
+        <v>11255902</v>
       </c>
       <c r="AE3" t="n">
-        <v>21966202</v>
+        <v>19248175</v>
       </c>
       <c r="AF3" t="n">
-        <v>11256</v>
+        <v>23870</v>
       </c>
       <c r="AG3" t="n">
-        <v>6598328</v>
+        <v>4609483</v>
       </c>
       <c r="AH3" t="n">
-        <v>6598328</v>
+        <v>4609483</v>
       </c>
       <c r="AI3" t="n">
-        <v>336445</v>
+        <v>245125</v>
       </c>
       <c r="AJ3" t="n">
-        <v>7728711</v>
+        <v>8138120</v>
       </c>
       <c r="AK3" t="n">
-        <v>1236126</v>
+        <v>656271</v>
       </c>
       <c r="AL3" t="n">
-        <v>693120</v>
+        <v>963273</v>
       </c>
       <c r="AM3" t="n">
-        <v>5799465</v>
+        <v>6518576</v>
       </c>
       <c r="AN3" t="n">
-        <v>59889193</v>
+        <v>54378041</v>
       </c>
       <c r="AO3" t="n">
-        <v>37532526</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>35199297</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>5000</v>
+      </c>
       <c r="AQ3" t="n">
-        <v>24812</v>
+        <v>4812</v>
       </c>
       <c r="AR3" t="n">
-        <v>24812</v>
+        <v>4812</v>
       </c>
       <c r="AS3" t="n">
-        <v>8793360</v>
+        <v>9617101</v>
       </c>
       <c r="AT3" t="n">
-        <v>4890968</v>
+        <v>4962188</v>
       </c>
       <c r="AU3" t="n">
-        <v>3902392</v>
+        <v>4654913</v>
       </c>
       <c r="AV3" t="n">
-        <v>28672323</v>
+        <v>25551019</v>
       </c>
       <c r="AW3" t="n">
-        <v>28672323</v>
+        <v>25551019</v>
       </c>
       <c r="AX3" t="n">
-        <v>22368</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>27352364</v>
+        <v>25380509</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1292591</v>
+        <v>170510</v>
       </c>
       <c r="BA3" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>22356666</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
+        <v>19178744</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>780000</v>
+      </c>
       <c r="BD3" t="n">
-        <v>336151</v>
+        <v>458803</v>
       </c>
       <c r="BE3" t="n">
-        <v>2492160</v>
+        <v>2491453</v>
       </c>
       <c r="BF3" t="n">
-        <v>445816</v>
+        <v>96928</v>
       </c>
       <c r="BG3" t="n">
-        <v>804414</v>
+        <v>843489</v>
       </c>
       <c r="BH3" t="n">
-        <v>804414</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
+        <v>843489</v>
+      </c>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="n">
-        <v>428086</v>
+        <v>319535</v>
       </c>
       <c r="BL3" t="n">
-        <v>2196192</v>
+        <v>2288599</v>
       </c>
       <c r="BM3" t="n">
-        <v>9845965</v>
+        <v>8684012</v>
       </c>
       <c r="BN3" t="n">
-        <v>5807882</v>
+        <v>3995925</v>
       </c>
       <c r="BO3" t="n">
-        <v>645492</v>
+        <v>400492</v>
       </c>
       <c r="BP3" t="n">
-        <v>5162390</v>
+        <v>3595433</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5151369</v>
+        <v>3585928</v>
       </c>
       <c r="BR3" t="n">
-        <v>11021</v>
+        <v>9505</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6752762</v>
+        <v>6796750</v>
       </c>
       <c r="D4" t="n">
-        <v>6752762</v>
+        <v>6796750</v>
       </c>
       <c r="E4" t="n">
-        <v>12269952</v>
+        <v>13924887</v>
       </c>
       <c r="F4" t="n">
-        <v>15865385</v>
+        <v>19087277</v>
       </c>
       <c r="G4" t="n">
-        <v>11435076</v>
+        <v>13303923</v>
       </c>
       <c r="H4" t="n">
-        <v>36917562</v>
+        <v>41184560</v>
       </c>
       <c r="I4" t="n">
-        <v>-69431</v>
+        <v>390464</v>
       </c>
       <c r="J4" t="n">
-        <v>11435076</v>
+        <v>13303923</v>
       </c>
       <c r="K4" t="n">
-        <v>21052177</v>
+        <v>22097283</v>
       </c>
       <c r="L4" t="n">
-        <v>32308079</v>
+        <v>34586232</v>
       </c>
       <c r="M4" t="n">
-        <v>21572963</v>
+        <v>22720675</v>
       </c>
       <c r="N4" t="n">
-        <v>520786</v>
+        <v>623392</v>
       </c>
       <c r="O4" t="n">
-        <v>21052177</v>
+        <v>22097283</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
         <v>66725</v>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
       <c r="S4" t="n">
-        <v>1206447</v>
+        <v>1120775</v>
       </c>
       <c r="T4" t="n">
-        <v>8769388</v>
+        <v>9043013</v>
       </c>
       <c r="U4" t="n">
-        <v>4048912</v>
+        <v>4075287</v>
       </c>
       <c r="V4" t="n">
-        <v>4048912</v>
+        <v>4075287</v>
       </c>
       <c r="W4" t="n">
-        <v>32805078</v>
+        <v>37168518</v>
       </c>
       <c r="X4" t="n">
-        <v>13556903</v>
+        <v>15202316</v>
       </c>
       <c r="Y4" t="n">
-        <v>338000</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
+        <v>64871</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1482591</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1165903</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>12488949</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>12488949</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>21966202</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>11256</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>6598328</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>6598328</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>336445</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>7728711</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1236126</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>693120</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5799465</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>59889193</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>37532526</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>24812</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>24812</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8793360</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4890968</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3902392</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>28672323</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>28672323</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>22368</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>27352364</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1292591</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>22356666</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="n">
+        <v>336151</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2492160</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>445816</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>804414</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>804414</v>
+      </c>
+      <c r="BI4" t="n">
         <v>0</v>
       </c>
-      <c r="AA4" t="n">
-        <v>1037803</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1263198</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>11255902</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>11255902</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>19248175</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>23870</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4609483</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>4609483</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>245125</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>8138120</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>656271</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>963273</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>6518576</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>54378041</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>35199297</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>4812</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4812</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9617101</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4962188</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4654913</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>25551019</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>25551019</v>
-      </c>
-      <c r="AX4" t="n">
+      <c r="BJ4" t="n">
         <v>0</v>
       </c>
-      <c r="AY4" t="n">
-        <v>25380509</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>170510</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>19178744</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>780000</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>458803</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>2491453</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>96928</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>843489</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>843489</v>
-      </c>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="n">
-        <v>319535</v>
+        <v>428086</v>
       </c>
       <c r="BL4" t="n">
-        <v>2288599</v>
+        <v>2196192</v>
       </c>
       <c r="BM4" t="n">
-        <v>8684012</v>
+        <v>9845965</v>
       </c>
       <c r="BN4" t="n">
-        <v>3995925</v>
+        <v>5807882</v>
       </c>
       <c r="BO4" t="n">
-        <v>400492</v>
+        <v>645492</v>
       </c>
       <c r="BP4" t="n">
-        <v>3595433</v>
+        <v>5162390</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3585928</v>
+        <v>5151369</v>
       </c>
       <c r="BR4" t="n">
-        <v>9505</v>
+        <v>11021</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45657</v>
+      </c>
+      <c r="B5" t="n">
+        <v>217000</v>
+      </c>
       <c r="C5" t="n">
-        <v>6600000</v>
+        <v>6579750</v>
       </c>
       <c r="D5" t="n">
-        <v>6600000</v>
+        <v>6796750</v>
       </c>
       <c r="E5" t="n">
-        <v>8576355</v>
+        <v>17418751</v>
       </c>
       <c r="F5" t="n">
-        <v>12063930</v>
+        <v>21695973</v>
       </c>
       <c r="G5" t="n">
-        <v>9178421</v>
+        <v>9511421</v>
       </c>
       <c r="H5" t="n">
-        <v>29930250</v>
+        <v>43223594</v>
       </c>
       <c r="I5" t="n">
-        <v>-3149556</v>
+        <v>-3617375</v>
       </c>
       <c r="J5" t="n">
-        <v>9178421</v>
+        <v>9511421</v>
       </c>
       <c r="K5" t="n">
-        <v>17866320</v>
+        <v>21527621</v>
       </c>
       <c r="L5" t="n">
-        <v>26710173</v>
+        <v>35379303</v>
       </c>
       <c r="M5" t="n">
-        <v>18270744</v>
+        <v>22035658</v>
       </c>
       <c r="N5" t="n">
-        <v>404424</v>
+        <v>508037</v>
       </c>
       <c r="O5" t="n">
-        <v>17866320</v>
-      </c>
-      <c r="P5" t="n">
-        <v>7464720</v>
-      </c>
+        <v>21527621</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>3779272</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>66725</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1060360</v>
+      </c>
       <c r="S5" t="n">
-        <v>860722</v>
+        <v>277718</v>
       </c>
       <c r="T5" t="n">
-        <v>7464720</v>
+        <v>9043013</v>
       </c>
       <c r="U5" t="n">
-        <v>133500</v>
+        <v>4075287</v>
       </c>
       <c r="V5" t="n">
-        <v>133500</v>
+        <v>4075287</v>
       </c>
       <c r="W5" t="n">
-        <v>28389951</v>
+        <v>45426588</v>
       </c>
       <c r="X5" t="n">
-        <v>11091610</v>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+        <v>16996943</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
       <c r="Z5" t="n">
-        <v>17751</v>
+        <v>156290</v>
       </c>
       <c r="AA5" t="n">
-        <v>973708</v>
+        <v>1934767</v>
       </c>
       <c r="AB5" t="n">
-        <v>1256298</v>
+        <v>1054203</v>
       </c>
       <c r="AC5" t="n">
-        <v>8843853</v>
+        <v>13851682</v>
       </c>
       <c r="AD5" t="n">
-        <v>8843853</v>
+        <v>13851682</v>
       </c>
       <c r="AE5" t="n">
-        <v>17298341</v>
+        <v>28429645</v>
       </c>
       <c r="AF5" t="n">
-        <v>13049</v>
+        <v>4960</v>
       </c>
       <c r="AG5" t="n">
-        <v>3220077</v>
+        <v>7844291</v>
       </c>
       <c r="AH5" t="n">
-        <v>3220077</v>
+        <v>7844291</v>
       </c>
       <c r="AI5" t="n">
-        <v>235431</v>
+        <v>366272</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8153569</v>
+        <v>10790849</v>
       </c>
       <c r="AK5" t="n">
-        <v>1982692</v>
+        <v>1779398</v>
       </c>
       <c r="AL5" t="n">
-        <v>465946</v>
+        <v>528317</v>
       </c>
       <c r="AM5" t="n">
-        <v>5704931</v>
+        <v>8483134</v>
       </c>
       <c r="AN5" t="n">
-        <v>46660695</v>
+        <v>67462246</v>
       </c>
       <c r="AO5" t="n">
-        <v>32511910</v>
+        <v>42649975</v>
       </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>4812</v>
+        <v>25499</v>
       </c>
       <c r="AR5" t="n">
-        <v>4812</v>
+        <v>25499</v>
       </c>
       <c r="AS5" t="n">
-        <v>8687899</v>
+        <v>12016200</v>
       </c>
       <c r="AT5" t="n">
-        <v>4982706</v>
+        <v>4794794</v>
       </c>
       <c r="AU5" t="n">
-        <v>3705193</v>
+        <v>7221406</v>
       </c>
       <c r="AV5" t="n">
-        <v>23800676</v>
+        <v>30542122</v>
       </c>
       <c r="AW5" t="n">
-        <v>23800676</v>
+        <v>30542122</v>
       </c>
       <c r="AX5" t="n">
-        <v>222764</v>
+        <v>145120</v>
       </c>
       <c r="AY5" t="n">
-        <v>23390221</v>
+        <v>28855265</v>
       </c>
       <c r="AZ5" t="n">
-        <v>187691</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
+        <v>1152762</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>388975</v>
+      </c>
       <c r="BB5" t="n">
-        <v>14148785</v>
+        <v>24812270</v>
       </c>
       <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
+      <c r="BD5" t="n">
+        <v>145003</v>
+      </c>
       <c r="BE5" t="n">
-        <v>1158248</v>
+        <v>3499302</v>
       </c>
       <c r="BF5" t="n">
-        <v>76416</v>
+        <v>623707</v>
       </c>
       <c r="BG5" t="n">
-        <v>896521</v>
+        <v>1138510</v>
       </c>
       <c r="BH5" t="n">
-        <v>896521</v>
+        <v>867610</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>69075</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>201825</v>
       </c>
       <c r="BK5" t="n">
-        <v>237856</v>
+        <v>1150891</v>
       </c>
       <c r="BL5" t="n">
-        <v>726442</v>
+        <v>2001764</v>
       </c>
       <c r="BM5" t="n">
-        <v>7165235</v>
+        <v>11330379</v>
       </c>
       <c r="BN5" t="n">
-        <v>3888067</v>
+        <v>4922714</v>
       </c>
       <c r="BO5" t="n">
-        <v>400492</v>
+        <v>645492</v>
       </c>
       <c r="BP5" t="n">
-        <v>3487575</v>
+        <v>4277222</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3484012</v>
+        <v>4272326</v>
       </c>
       <c r="BR5" t="n">
-        <v>3562</v>
+        <v>4896</v>
       </c>
     </row>
   </sheetData>
@@ -2697,586 +2697,586 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-2038309</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-1060360</v>
-      </c>
+        <v>-6762810</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>-6999945</v>
-      </c>
-      <c r="E2" t="n">
-        <v>9666972</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
+        <v>-1813703</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>-12301279</v>
+        <v>-13424829</v>
       </c>
       <c r="H2" t="n">
-        <v>4277222</v>
+        <v>3888066</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>5162390</v>
+        <v>12832705</v>
       </c>
       <c r="K2" t="n">
-        <v>-885168</v>
+        <v>-8944639</v>
       </c>
       <c r="L2" t="n">
-        <v>1753829</v>
+        <v>-747200</v>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
-        <v>-679675</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-1060360</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-1060360</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>3493864</v>
+        <v>-747200</v>
       </c>
       <c r="S2" t="n">
-        <v>826837</v>
+        <v>1066503</v>
       </c>
       <c r="T2" t="n">
-        <v>2667027</v>
+        <v>-1813703</v>
       </c>
       <c r="U2" t="n">
-        <v>-6999945</v>
-      </c>
-      <c r="V2" t="n">
-        <v>9666972</v>
-      </c>
+        <v>-1813703</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>-12901967</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-1</v>
-      </c>
+        <v>-14859458</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>-687</v>
+        <v>-372</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-687</v>
+        <v>-372</v>
       </c>
       <c r="AB2" t="n">
-        <v>-600000</v>
+        <v>-1434257</v>
       </c>
       <c r="AC2" t="n">
-        <v>-600000</v>
+        <v>-1434257</v>
       </c>
       <c r="AD2" t="n">
-        <v>-5773350</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+        <v>-4209343</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
       <c r="AF2" t="n">
-        <v>-5773350</v>
+        <v>-4209343</v>
       </c>
       <c r="AG2" t="n">
-        <v>-6527929</v>
+        <v>-9215486</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-6527929</v>
+        <v>-9215486</v>
       </c>
       <c r="AJ2" t="n">
-        <v>10262970</v>
+        <v>6662019</v>
       </c>
       <c r="AK2" t="n">
-        <v>-297634</v>
+        <v>-210178</v>
       </c>
       <c r="AL2" t="n">
-        <v>-656741</v>
+        <v>-240125</v>
       </c>
       <c r="AM2" t="n">
-        <v>1556031</v>
+        <v>1934551</v>
       </c>
       <c r="AN2" t="n">
-        <v>-446450</v>
+        <v>895423</v>
       </c>
       <c r="AO2" t="n">
-        <v>2131810</v>
+        <v>2353490</v>
       </c>
       <c r="AP2" t="n">
-        <v>2683669</v>
+        <v>84928</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-334096</v>
+        <v>-28188</v>
       </c>
       <c r="AR2" t="n">
-        <v>-2478902</v>
+        <v>-1371102</v>
       </c>
       <c r="AS2" t="n">
-        <v>621618</v>
+        <v>240125</v>
       </c>
       <c r="AT2" t="n">
-        <v>53175</v>
+        <v>33046</v>
       </c>
       <c r="AU2" t="n">
-        <v>80279</v>
+        <v>83436</v>
       </c>
       <c r="AV2" t="n">
-        <v>7208640</v>
+        <v>3766278</v>
       </c>
       <c r="AW2" t="n">
-        <v>7208640</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>282568</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+        <v>3766278</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>1331978</v>
+        <v>1054238</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>729880</v>
+        <v>-5324342</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>-4609483</v>
+        <v>-6496924</v>
       </c>
       <c r="E3" t="n">
-        <v>7750000</v>
+        <v>10284221</v>
       </c>
       <c r="F3" t="n">
-        <v>300000</v>
+        <v>1355005</v>
       </c>
       <c r="G3" t="n">
-        <v>-5972770</v>
+        <v>-7450065</v>
       </c>
       <c r="H3" t="n">
-        <v>5162390</v>
+        <v>3595433</v>
       </c>
       <c r="I3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>3595433</v>
+        <v>3888066</v>
       </c>
       <c r="K3" t="n">
-        <v>1566958</v>
+        <v>-292634</v>
       </c>
       <c r="L3" t="n">
-        <v>1557078</v>
-      </c>
-      <c r="M3" t="n">
-        <v>-3009922</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-378478</v>
-      </c>
+        <v>6531708</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>300000</v>
+        <v>1355005</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>300000</v>
+        <v>1355005</v>
       </c>
       <c r="R3" t="n">
-        <v>1635556</v>
+        <v>5176703</v>
       </c>
       <c r="S3" t="n">
-        <v>-1504961</v>
+        <v>1389406</v>
       </c>
       <c r="T3" t="n">
-        <v>3140517</v>
+        <v>3787297</v>
       </c>
       <c r="U3" t="n">
-        <v>-4609483</v>
+        <v>-6496924</v>
       </c>
       <c r="V3" t="n">
-        <v>7750000</v>
+        <v>10284221</v>
       </c>
       <c r="W3" t="n">
-        <v>-6692770</v>
+        <v>-8950065</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>-20000</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-20000</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-700000</v>
+        <v>-1500000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-700000</v>
+        <v>-1500000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1159103</v>
+        <v>-2397106</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1159103</v>
+        <v>-2397106</v>
       </c>
       <c r="AG3" t="n">
-        <v>-4813667</v>
+        <v>-5052959</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-4813667</v>
+        <v>-5052959</v>
       </c>
       <c r="AJ3" t="n">
-        <v>6702650</v>
+        <v>2125723</v>
       </c>
       <c r="AK3" t="n">
-        <v>-392229</v>
+        <v>-68869</v>
       </c>
       <c r="AL3" t="n">
-        <v>-491125</v>
+        <v>-300295</v>
       </c>
       <c r="AM3" t="n">
-        <v>-989397</v>
+        <v>-4005613</v>
       </c>
       <c r="AN3" t="n">
-        <v>-199371</v>
+        <v>-2587950</v>
       </c>
       <c r="AO3" t="n">
-        <v>1059886</v>
+        <v>555362</v>
       </c>
       <c r="AP3" t="n">
-        <v>-719111</v>
+        <v>813645</v>
       </c>
       <c r="AQ3" t="n">
-        <v>39075</v>
+        <v>53032</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1169876</v>
+        <v>-2839702</v>
       </c>
       <c r="AS3" t="n">
-        <v>558420</v>
+        <v>153065</v>
       </c>
       <c r="AT3" t="n">
-        <v>49132</v>
+        <v>38688</v>
       </c>
       <c r="AU3" t="n">
-        <v>-22255</v>
+        <v>429812</v>
       </c>
       <c r="AV3" t="n">
-        <v>6271552</v>
+        <v>4884829</v>
       </c>
       <c r="AW3" t="n">
-        <v>6271552</v>
+        <v>4884829</v>
       </c>
       <c r="AX3" t="n">
-        <v>187523</v>
+        <v>-476554</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1412407</v>
+        <v>1470660</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-5324342</v>
+        <v>729880</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-6496924</v>
+        <v>-4609483</v>
       </c>
       <c r="E4" t="n">
-        <v>10284221</v>
+        <v>7750000</v>
       </c>
       <c r="F4" t="n">
-        <v>1355005</v>
+        <v>300000</v>
       </c>
       <c r="G4" t="n">
-        <v>-7450065</v>
+        <v>-5972770</v>
       </c>
       <c r="H4" t="n">
+        <v>5162390</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J4" t="n">
         <v>3595433</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3888066</v>
-      </c>
       <c r="K4" t="n">
-        <v>-292634</v>
+        <v>1566958</v>
       </c>
       <c r="L4" t="n">
-        <v>6531708</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+        <v>1557078</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-3009922</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-378478</v>
+      </c>
       <c r="O4" t="n">
-        <v>1355005</v>
+        <v>300000</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>1355005</v>
+        <v>300000</v>
       </c>
       <c r="R4" t="n">
-        <v>5176703</v>
+        <v>1635556</v>
       </c>
       <c r="S4" t="n">
-        <v>1389406</v>
+        <v>-1504961</v>
       </c>
       <c r="T4" t="n">
-        <v>3787297</v>
+        <v>3140517</v>
       </c>
       <c r="U4" t="n">
-        <v>-6496924</v>
+        <v>-4609483</v>
       </c>
       <c r="V4" t="n">
-        <v>10284221</v>
+        <v>7750000</v>
       </c>
       <c r="W4" t="n">
-        <v>-8950065</v>
+        <v>-6692770</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-20000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-20000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1500000</v>
+        <v>-700000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1500000</v>
+        <v>-700000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2397106</v>
+        <v>-1159103</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-2397106</v>
+        <v>-1159103</v>
       </c>
       <c r="AG4" t="n">
-        <v>-5052959</v>
+        <v>-4813667</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-5052959</v>
+        <v>-4813667</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2125723</v>
+        <v>6702650</v>
       </c>
       <c r="AK4" t="n">
-        <v>-68869</v>
+        <v>-392229</v>
       </c>
       <c r="AL4" t="n">
-        <v>-300295</v>
+        <v>-491125</v>
       </c>
       <c r="AM4" t="n">
-        <v>-4005613</v>
+        <v>-989397</v>
       </c>
       <c r="AN4" t="n">
-        <v>-2587950</v>
+        <v>-199371</v>
       </c>
       <c r="AO4" t="n">
-        <v>555362</v>
+        <v>1059886</v>
       </c>
       <c r="AP4" t="n">
-        <v>813645</v>
+        <v>-719111</v>
       </c>
       <c r="AQ4" t="n">
-        <v>53032</v>
+        <v>39075</v>
       </c>
       <c r="AR4" t="n">
-        <v>-2839702</v>
+        <v>-1169876</v>
       </c>
       <c r="AS4" t="n">
-        <v>153065</v>
+        <v>558420</v>
       </c>
       <c r="AT4" t="n">
-        <v>38688</v>
+        <v>49132</v>
       </c>
       <c r="AU4" t="n">
-        <v>429812</v>
+        <v>-22255</v>
       </c>
       <c r="AV4" t="n">
-        <v>4884829</v>
+        <v>6271552</v>
       </c>
       <c r="AW4" t="n">
-        <v>4884829</v>
+        <v>6271552</v>
       </c>
       <c r="AX4" t="n">
-        <v>-476554</v>
+        <v>187523</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1470660</v>
+        <v>1412407</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-6762810</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>-2038309</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1060360</v>
+      </c>
       <c r="D5" t="n">
-        <v>-1813703</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+        <v>-6999945</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9666972</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
       <c r="G5" t="n">
-        <v>-13424829</v>
+        <v>-12301279</v>
       </c>
       <c r="H5" t="n">
-        <v>3888066</v>
+        <v>4277222</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>12832705</v>
+        <v>5162390</v>
       </c>
       <c r="K5" t="n">
-        <v>-8944639</v>
+        <v>-885168</v>
       </c>
       <c r="L5" t="n">
-        <v>-747200</v>
+        <v>1753829</v>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>-679675</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-1060360</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-1060360</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
       <c r="R5" t="n">
-        <v>-747200</v>
+        <v>3493864</v>
       </c>
       <c r="S5" t="n">
-        <v>1066503</v>
+        <v>826837</v>
       </c>
       <c r="T5" t="n">
-        <v>-1813703</v>
+        <v>2667027</v>
       </c>
       <c r="U5" t="n">
-        <v>-1813703</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
+        <v>-6999945</v>
+      </c>
+      <c r="V5" t="n">
+        <v>9666972</v>
+      </c>
       <c r="W5" t="n">
-        <v>-14859458</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
+        <v>-12901967</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Y5" t="n">
-        <v>-372</v>
+        <v>-687</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-372</v>
+        <v>-687</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1434257</v>
+        <v>-600000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1434257</v>
+        <v>-600000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-4209343</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
+        <v>-5773350</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>-4209343</v>
+        <v>-5773350</v>
       </c>
       <c r="AG5" t="n">
-        <v>-9215486</v>
+        <v>-6527929</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-9215486</v>
+        <v>-6527929</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6662019</v>
+        <v>10262970</v>
       </c>
       <c r="AK5" t="n">
-        <v>-210178</v>
+        <v>-297634</v>
       </c>
       <c r="AL5" t="n">
-        <v>-240125</v>
+        <v>-656741</v>
       </c>
       <c r="AM5" t="n">
-        <v>1934551</v>
+        <v>1556031</v>
       </c>
       <c r="AN5" t="n">
-        <v>895423</v>
+        <v>-446450</v>
       </c>
       <c r="AO5" t="n">
-        <v>2353490</v>
+        <v>2131810</v>
       </c>
       <c r="AP5" t="n">
-        <v>84928</v>
+        <v>2683669</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-28188</v>
+        <v>-334096</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1371102</v>
+        <v>-2478902</v>
       </c>
       <c r="AS5" t="n">
-        <v>240125</v>
+        <v>621618</v>
       </c>
       <c r="AT5" t="n">
-        <v>33046</v>
+        <v>53175</v>
       </c>
       <c r="AU5" t="n">
-        <v>83436</v>
+        <v>80279</v>
       </c>
       <c r="AV5" t="n">
-        <v>3766278</v>
+        <v>7208640</v>
       </c>
       <c r="AW5" t="n">
-        <v>3766278</v>
-      </c>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
+        <v>7208640</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>282568</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>1054238</v>
+        <v>1331978</v>
       </c>
     </row>
   </sheetData>
@@ -3821,182 +3821,182 @@
       </c>
       <c r="DB1" t="inlineStr">
         <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
           <t>shortName</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Bruno Mario Pianetti', 'age': 62, 'title': 'Chairman of the Board &amp; CEO', 'yearBorn': 1963, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Michele  Pagani', 'title': 'Chief Financial Officer', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Mirko  Mare', 'age': 51, 'title': 'MD, COO &amp; Director', 'yearBorn': 1974, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Bruno Mario Pianetti', 'age': 62, 'title': 'Chairman &amp; CEO', 'yearBorn': 1963, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Michele  Pagani', 'title': 'Chief Financial Officer', 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -4101,34 +4101,34 @@
         <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>3.56</v>
+        <v>3.68</v>
       </c>
       <c r="V2" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="W2" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="X2" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.56</v>
+        <v>3.68</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="AC2" t="n">
         <v>0.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="AE2" t="n">
         <v>1778457600</v>
@@ -4137,10 +4137,10 @@
         <v>1.1759</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.573</v>
+        <v>0.516</v>
       </c>
       <c r="AH2" t="n">
-        <v>36</v>
+        <v>36.199997</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -4158,16 +4158,16 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="AO2" t="n">
-        <v>3.72</v>
+        <v>3.78</v>
       </c>
       <c r="AP2" t="n">
-        <v>23687100</v>
+        <v>23818694</v>
       </c>
       <c r="AQ2" t="n">
-        <v>24081885</v>
+        <v>24213480</v>
       </c>
       <c r="AR2" t="n">
         <v>3.52</v>
@@ -4182,19 +4182,19 @@
         <v>3.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.5572376</v>
+        <v>0.5603334</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.8236</v>
+        <v>3.7628</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.9126</v>
+        <v>3.8846</v>
       </c>
       <c r="AY2" t="n">
         <v>0.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.028089888</v>
+        <v>0.027173912</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>42329076</v>
+        <v>42460672</v>
       </c>
       <c r="BD2" t="n">
         <v>0.015800001</v>
@@ -4229,7 +4229,7 @@
         <v>3.245</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.1093991</v>
+        <v>1.1155624</v>
       </c>
       <c r="BL2" t="n">
         <v>1767139200</v>
@@ -4250,16 +4250,16 @@
         <v>0.1</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.996</v>
+        <v>0.999</v>
       </c>
       <c r="BS2" t="n">
-        <v>5.039</v>
+        <v>5.054</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0.114427865</v>
+        <v>-0.031578958</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BV2" t="n">
         <v>0.1</v>
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="BY2" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
@@ -4375,140 +4375,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DB2" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>-0.06000018</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>3.62 - 3.62</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0.099999905</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0.028409064</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>3.52 - 4.38</t>
+        </is>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.7600002</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>-0.17351604</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-3.1578958</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>-0.1428001</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-0.037950486</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.26460004</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.06811513</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>Planetel Srl</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="DV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1610607600000</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>Planetel S.p.A.</t>
+        </is>
+      </c>
+      <c r="EA2" t="n">
+        <v>-1.6304396</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>finmb_182551002</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="EF2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EJ2" t="n">
+        <v>1782109700</v>
+      </c>
+      <c r="EK2" t="inlineStr">
         <is>
           <t>Planetel S.p.A.               A</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>1780381637</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>1.1235945</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>finmb_182551002</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="DN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>1610607600000</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.03999996</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>3.6 - 3.6</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.07999992</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0.022727251</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>3.52 - 4.38</t>
-        </is>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.7800002</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.17808223</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-11.442786</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.22360015</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.05847896</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.31260014</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0.07989576</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>Planetel Srl</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="EJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>Planetel S.p.A.</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr"/>
